--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -545,14 +545,14 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
@@ -1189,7 +1189,7 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;lt VIM_NORMAL_BASE SPACE</t>
+&amp;none</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1208,7 +1208,7 @@
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;mo BLUETOOTH</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1220,13 +1220,13 @@
       <c r="K13" s="7" t="inlineStr">
         <is>
           <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1263,11 +1263,7 @@
           <t>LAlt</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>SPACE</t>
-        </is>
-      </c>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
           <t>SPACE</t>
@@ -1281,22 +1277,18 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>ENTER</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
           <t>L7</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>L2</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -1331,11 +1323,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="9" t="inlineStr">
         <is>
           <t>L2</t>
@@ -1357,11 +1345,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K15" s="9" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1895,7 +1879,7 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;lt VIM_NORMAL_SYM SPACE</t>
+&amp;none</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1914,7 +1898,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -1932,7 +1916,7 @@
       <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;mo VIM_NORMAL_SYM</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -1965,11 +1949,7 @@
           <t>▽</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>SPACE</t>
-        </is>
-      </c>
+      <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="9" t="inlineStr">
         <is>
           <t>SPACE</t>
@@ -1977,14 +1957,14 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
+      <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
@@ -2009,11 +1989,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
+      <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>L3</t>
@@ -2021,14 +1997,14 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6087,14 +6063,14 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
@@ -6731,7 +6707,7 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;lt VIM_NORMAL_BASE SPACE</t>
+&amp;none</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -6750,7 +6726,7 @@
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;mo BLUETOOTH</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -6762,13 +6738,13 @@
       <c r="K13" s="7" t="inlineStr">
         <is>
           <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
 &amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -6805,11 +6781,7 @@
           <t>&amp;kp LEFT_ALT</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
@@ -6823,22 +6795,18 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>&amp;mo VIM_NORMAL_BASE</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
           <t>&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt NUM_SYMBOL ENTER</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -6873,11 +6841,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
-        </is>
-      </c>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
@@ -6899,11 +6863,7 @@
           <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K15" s="9" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7437,7 +7397,7 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;lt VIM_NORMAL_SYM SPACE</t>
+&amp;none</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -7456,7 +7416,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -7474,7 +7434,7 @@
       <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;mo VIM_NORMAL_SYM</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -7507,11 +7467,7 @@
           <t>▽</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
-        </is>
-      </c>
+      <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
@@ -7519,14 +7475,14 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_NORMAL_SYM</t>
-        </is>
-      </c>
+      <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr">
         <is>
           <t>▽</t>
@@ -7551,11 +7507,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
-        </is>
-      </c>
+      <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
@@ -7563,14 +7515,14 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr">
         <is>
           <t>〃</t>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -1922,7 +1922,7 @@
       <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
@@ -1965,11 +1965,7 @@
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M26" s="9" t="inlineStr"/>
       <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2005,11 +2001,7 @@
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M27" s="9" t="inlineStr"/>
       <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2781,7 +2773,7 @@
       <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
@@ -2824,11 +2816,7 @@
       </c>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2864,11 +2852,7 @@
       </c>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3287,7 +3271,7 @@
       <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
@@ -3322,11 +3306,7 @@
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M54" s="9" t="inlineStr"/>
       <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
@@ -7440,7 +7420,7 @@
       <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
@@ -7483,11 +7463,7 @@
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M26" s="9" t="inlineStr"/>
       <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7523,11 +7499,7 @@
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M27" s="9" t="inlineStr"/>
       <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -8334,7 +8306,7 @@
       <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
@@ -8377,11 +8349,7 @@
       </c>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -8417,11 +8385,7 @@
       </c>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -8852,7 +8816,7 @@
       <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
@@ -8887,11 +8851,7 @@
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="M54" s="9" t="inlineStr"/>
       <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3312,7 +3312,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -3344,13 +3344,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -3371,7 +3371,7 @@
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -3395,29 +3395,52 @@
       <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+&amp;macro_vim_visual_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
       <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃C
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃V
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3428,7 +3451,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -3440,7 +3463,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -3452,7 +3475,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -3461,391 +3484,470 @@
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>⇧↓</t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
+          <t>⇧↑</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>⇧→</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃HOME</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃END</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
+          <t>pos 21
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 32
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 33
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 24
+&amp;kp LS(LC(LEFT))</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
+      <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 25
+&amp;kp F3</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>pos 29
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃←</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
       <c r="I63" s="9" t="inlineStr"/>
-      <c r="J63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3854,32 +3956,32 @@
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 15
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 16
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
-&amp;none</t>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
         </is>
       </c>
     </row>
@@ -3898,304 +4000,324 @@
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>🖱左</t>
-        </is>
-      </c>
+      <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>🖱右</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>⇧END</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>🖱戻</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>🖱進</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;kp F1</t>
+          <t>pos 30
+&amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp F2</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp F3</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;kp F4</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;kp F5</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;kp F6</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;kp F7</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>pos 7
-&amp;kp F8</t>
+          <t>pos 39
+&amp;none</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>pos 8
-&amp;kp F9</t>
+          <t>pos 40
+&amp;none</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;kp F10</t>
+          <t>pos 41
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -4205,442 +4327,442 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr"/>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;kp F7</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;kp F8</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;kp F9</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 30
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4651,1067 +4773,949 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>BT0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>BT1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>BT2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>BT3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>BT4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>USB出力</t>
-        </is>
-      </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>BT全解除</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>BT解除</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>BLE出力</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1">
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃C
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃V
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↓</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↑</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>⇧→</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
+      <c r="N93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃HOME</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃END</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃←</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 36
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="9" t="inlineStr"/>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="9" t="inlineStr"/>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr"/>
-      <c r="N104" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Shift+</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>⇧END</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
       <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
-        </is>
-      </c>
+      <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -5722,7 +5726,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5755,13 +5759,13 @@
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -5773,13 +5777,13 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5789,11 +5793,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
@@ -5801,19 +5801,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
-        </is>
-      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5824,7 +5824,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5863,7 +5863,7 @@
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -5875,13 +5875,13 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5891,11 +5891,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -5904,14 +5900,18 @@
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -6015,16 +6015,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A45:N45"/>
     <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A102:N102"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8857,7 +8857,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -8889,13 +8889,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -8916,7 +8916,7 @@
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -8940,7 +8940,7 @@
       <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
+&amp;macro_vim_visual_p</t>
         </is>
       </c>
     </row>
@@ -8951,18 +8951,34 @@
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
       <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_y</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_p</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -8973,7 +8989,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -8985,7 +9001,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -8997,7 +9013,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -9006,225 +9022,262 @@
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(DOWN)</t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo MOUSE_SCROLL</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>&amp;kp LS(UP)</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(RIGHT)</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[1]
+▸ &amp;kp LS(LC(HOME))</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[1]
+▸ &amp;kp LS(LC(END))</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
+          <t>pos 20
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
+          <t>pos 21
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 32
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 33
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 24
+&amp;kp LS(LC(LEFT))</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
+      <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 25
+&amp;kp F3</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
+          <t>pos 29
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -9234,163 +9287,205 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_exit</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(LEFT))</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
       <c r="I63" s="9" t="inlineStr"/>
-      <c r="J63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F3</t>
+        </is>
+      </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -9399,36 +9494,36 @@
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 15
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 16
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -9437,310 +9532,342 @@
       <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr"/>
       <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB1</t>
-        </is>
-      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB2</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(HOME)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[1]
+▸ &amp;kp LS(END)</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[1]
+▸ &amp;kp LS(HOME)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;kp F1</t>
+          <t>pos 30
+&amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp F2</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp F3</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;kp F4</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;kp F5</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;kp F6</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;kp F7</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>pos 7
-&amp;kp F8</t>
+          <t>pos 39
+&amp;none</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>pos 8
-&amp;kp F9</t>
+          <t>pos 40
+&amp;none</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;kp F10</t>
+          <t>pos 41
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -9750,442 +9877,442 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F1</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F2</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F4</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F5</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr"/>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;kp F7</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;kp F8</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;kp F9</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F6</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F7</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F8</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F9</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 30
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 33
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
+          <t>pos 38
+&amp;none</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10196,423 +10323,423 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;out OUT_USB</t>
-        </is>
-      </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 31
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 32
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>pos 6
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>pos 7
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>pos 8
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
+          <t>pos 41
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -10623,645 +10750,522 @@
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_y</t>
-        </is>
-      </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="N93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[1]
-▸ &amp;kp LS(LC(HOME))</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[1]
-▸ &amp;kp LS(LC(END))</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 36
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 37
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr"/>
-      <c r="N104" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[1]
-▸ &amp;kp LS(END)</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
       <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[1]
-▸ &amp;kp LS(HOME)</t>
-        </is>
-      </c>
+      <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -11272,7 +11276,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11305,13 +11309,13 @@
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -11323,13 +11327,13 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11339,11 +11343,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
@@ -11351,19 +11351,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11374,7 +11374,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11413,7 +11413,7 @@
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -11425,13 +11425,13 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11441,11 +11441,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -11454,14 +11450,18 @@
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11565,16 +11565,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A45:N45"/>
     <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A102:N102"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5344,7 +5344,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5401,7 +5401,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -10894,7 +10898,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -10951,7 +10955,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5736,7 +5736,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5748,7 +5748,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5798,9 +5798,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -5834,7 +5842,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5846,7 +5854,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -5896,9 +5904,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -11290,7 +11306,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11302,7 +11318,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -11352,9 +11368,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -11388,7 +11412,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11400,7 +11424,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -11450,9 +11474,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5344,7 +5344,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5401,7 +5401,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -5732,7 +5736,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5744,7 +5748,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5794,9 +5798,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -5830,7 +5842,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5842,7 +5854,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -5892,9 +5904,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -10894,7 +10914,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -10951,7 +10971,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -11282,7 +11306,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11294,7 +11318,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -11344,9 +11368,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -11380,7 +11412,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11392,7 +11424,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -11442,9 +11474,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
